--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/bio-bio.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/bio-bio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M310"/>
+  <dimension ref="A1:M311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>32288.59</v>
+        <v>32122.69</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>902.05</v>
+        <v>893.04</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1800.32</v>
+        <v>1782.35</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>17633.83</v>
+        <v>17457.85</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2184.91</v>
+        <v>2163.11</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3980.22</v>
+        <v>3938.54</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3039.86</v>
+        <v>3023.25</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>775.86</v>
+        <v>771.62</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2041.2</v>
+        <v>2030.05</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6974.43</v>
+        <v>6936.31</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>10765.91</v>
+        <v>10645.96</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>9295.99</v>
+        <v>9245.08</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4458.21</v>
+        <v>4452.53</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>20751.23</v>
+        <v>20825.29</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1246.65</v>
+        <v>1250.75</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>14950.15</v>
+        <v>14999.32</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>12264.91</v>
+        <v>12476.62</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4749.86</v>
+        <v>4831.85</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5290.6</v>
+        <v>5315.24</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2475.77</v>
+        <v>2487.3</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>9990.74</v>
+        <v>10037.26</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>4158.98</v>
+        <v>4188.96</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>4632.91</v>
+        <v>4624.69</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>14096.44</v>
+        <v>14074.59</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>5833.58</v>
+        <v>5824.54</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3291.72</v>
+        <v>3286.61</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>23905.32</v>
+        <v>23868.27</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>4373.8</v>
+        <v>4367.02</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>13769.32</v>
+        <v>13747.98</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1792.19</v>
+        <v>1801.45</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>7494.41</v>
+        <v>7533.11</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1487.87</v>
+        <v>1468.64</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1085.94</v>
+        <v>1072.14</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1333.84</v>
+        <v>1316.9</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2227.54</v>
+        <v>2205.38</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3564.07</v>
+        <v>3528.6</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3480.75</v>
+        <v>3446.12</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2766.47</v>
+        <v>2760.48</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>34326.94</v>
+        <v>34252.65</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>761.42</v>
+        <v>752.61</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>760.03</v>
+        <v>753.6</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>3522</v>
+        <v>3519.17</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>9263</v>
+        <v>9287.559999999999</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>16442.28</v>
+        <v>16463.35</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>22266.78</v>
+        <v>22420.05</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>815.59</v>
+        <v>821.21</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>4763.99</v>
+        <v>4804.7</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1126.71</v>
+        <v>1136.34</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2438.68</v>
+        <v>2459.52</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1291.1</v>
+        <v>1302.14</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2856.46</v>
+        <v>2887.1</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>939.34</v>
+        <v>949.41</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>779.34</v>
+        <v>788.92</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>4839.97</v>
+        <v>4899.45</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>13364.95</v>
+        <v>13529.2</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>6865.73</v>
+        <v>6953.96</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3571.24</v>
+        <v>3590.77</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>12208.76</v>
+        <v>12275.52</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3100.22</v>
+        <v>3117.18</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3046.12</v>
+        <v>3062.78</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>9962.59</v>
+        <v>10017.07</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>12353.42</v>
+        <v>12037.97</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>11287.02</v>
+        <v>11124.38</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>3903.61</v>
+        <v>3895.92</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>20739.79</v>
+        <v>20739.92</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>32192.39</v>
+        <v>32192.59</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3881.38</v>
+        <v>3868.06</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2015.53</v>
+        <v>2004.88</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1687.87</v>
+        <v>1678.96</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>31785.27</v>
+        <v>31586.09</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>4423.09</v>
+        <v>4395.38</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>9154.200000000001</v>
+        <v>9096.84</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1601.99</v>
+        <v>1612.48</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1531.98</v>
+        <v>1542.02</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>810.6</v>
+        <v>830.3099999999999</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>7107.62</v>
+        <v>7280.47</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>8716.15</v>
+        <v>8928.1</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1742.57</v>
+        <v>1786.63</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1989.34</v>
+        <v>2039.63</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3164.3</v>
+        <v>3244.29</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>944.72</v>
+        <v>973.37</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>5814.72</v>
+        <v>5987.55</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2225.1</v>
+        <v>2217.17</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>16297.24</v>
+        <v>16344.45</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>3471.15</v>
+        <v>3502.72</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1014.1</v>
+        <v>1021.16</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>12740.33</v>
+        <v>12829.03</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>4577.67</v>
+        <v>4609.54</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>5928.91</v>
+        <v>5981.71</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>5054.09</v>
+        <v>5099.1</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>818.6</v>
+        <v>825.89</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>4861.91</v>
+        <v>4905.21</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>7498.98</v>
+        <v>7565.77</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1153.57</v>
+        <v>1152.38</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>10443.32</v>
+        <v>10368.5</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>5585.91</v>
+        <v>5577.69</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>962.26</v>
+        <v>956.41</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>3142.94</v>
+        <v>3123.84</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2982.8</v>
+        <v>2985.67</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>34047.57</v>
+        <v>34080.38</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>41420.78</v>
+        <v>43250.01</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2610.72</v>
+        <v>2726.02</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>47577.16</v>
+        <v>48959.11</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>4853.39</v>
+        <v>4933.38</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>6546.89</v>
+        <v>6462.6</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>5693.05</v>
+        <v>5619.76</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>3262.2</v>
+        <v>3239.17</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>16400.39</v>
+        <v>16284.65</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>6280.05</v>
+        <v>6393.91</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1403.81</v>
+        <v>1429.26</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>28274.79</v>
+        <v>28717.7</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2952.63</v>
+        <v>2952.48</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>775.4400000000001</v>
+        <v>771.97</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1591.56</v>
+        <v>1592.93</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>14836.9</v>
+        <v>14849.69</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1947.05</v>
+        <v>1955.09</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>34613.8</v>
+        <v>34756.79</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>5651.72</v>
+        <v>5675.07</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>2626.18</v>
+        <v>2618.94</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>26873.35</v>
+        <v>26799.23</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>20559.34</v>
+        <v>20502.62</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2353.34</v>
+        <v>2326.17</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3792.8</v>
+        <v>3749.01</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>10978.83</v>
+        <v>10815.07</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>5752.43</v>
+        <v>5666.63</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>36839.35</v>
+        <v>36289.88</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>8067.38</v>
+        <v>8021.04</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>4038.64</v>
+        <v>4012.76</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>5440.22</v>
+        <v>5405.37</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>7193.15</v>
+        <v>7162.16</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>11661.41</v>
+        <v>11492.7</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>24162.33</v>
+        <v>23812.77</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>10952.95</v>
+        <v>10794.49</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>3259.28</v>
+        <v>3212.13</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>4995.64</v>
+        <v>4888.16</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>15636.21</v>
+        <v>15272.37</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2821.49</v>
+        <v>2755.84</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1490.5</v>
+        <v>1455.81</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2759.67</v>
+        <v>2671.67</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="149">
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>4189-113-CM26</t>
+          <t>808211-30-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9562,17 +9562,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>69.160.300-8</t>
+          <t>69.160.400-4</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LEBU</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>CROBAK SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>77.071.404-4</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9597,13 +9597,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>10274.7</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>4189-137-CM26</t>
+          <t>808211-29-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9623,17 +9623,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>69.160.300-8</t>
+          <t>69.160.400-4</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LEBU</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>CROBAK SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>77.071.404-4</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9658,13 +9658,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>9158.18</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>808211-26-CM26</t>
+          <t>808211-28-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>808211-32-CM26</t>
+          <t>808211-27-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>808211-28-CM26</t>
+          <t>808211-26-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9841,13 +9841,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>808211-29-CM26</t>
+          <t>4189-137-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9867,17 +9867,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>69.160.400-4</t>
+          <t>69.160.300-8</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LEBU</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9887,12 +9887,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>CROBAK SPA</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.071.404-4</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -9902,13 +9902,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>2269.22</v>
+        <v>8866.16</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>808211-27-CM26</t>
+          <t>808211-32-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9963,13 +9963,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>2269.22</v>
+        <v>2196.86</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>808211-30-CM26</t>
+          <t>4189-113-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9989,17 +9989,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>69.160.400-4</t>
+          <t>69.160.300-8</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LEBU</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>CROBAK SPA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.071.404-4</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10024,13 +10024,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2269.22</v>
+        <v>9947.07</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1969-306-CM26</t>
+          <t>707422-48-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10050,17 +10050,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.004.068-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1112.78</v>
+        <v>16919.01</v>
       </c>
     </row>
     <row r="159">
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2423.77</v>
+        <v>2375.97</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>707422-48-CM26</t>
+          <t>1969-306-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10172,17 +10172,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.004.068-3</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Dirección Regional de Gendarmeria - Concepcion</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>17259.39</v>
+        <v>1090.83</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>10127.41</v>
+        <v>9856.23</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>8088.59</v>
+        <v>7872</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>69051.07000000001</v>
+        <v>67202.12</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>16290.92</v>
+        <v>15854.7</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1689.04</v>
+        <v>1703.37</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>783.5700000000001</v>
+        <v>790.22</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1346.37</v>
+        <v>1344.12</v>
       </c>
     </row>
     <row r="168">
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1680.61</v>
+        <v>1677.8</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2665-104-CM26</t>
+          <t>4081-127-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>69.150.101-9</t>
+          <t>69.151.001-8</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Dirección de Educación Municipal</t>
+          <t>Ilustre Municipalidad de Cabrero</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10741,12 +10741,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>GIOVANNI SEBASTIAN</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.737.293-0</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10756,13 +10756,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>4628.47</v>
+        <v>1677.8</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>4081-127-CM26</t>
+          <t>4858-289-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>69.151.001-8</t>
+          <t>69.160.700-3</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>I MUNICIPALIDAD DE TIRUA</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10802,12 +10802,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>1680.61</v>
+        <v>1849.29</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>4858-289-CM26</t>
+          <t>1084156-218-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10843,17 +10843,17 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>69.160.700-3</t>
+          <t>65.181.672-6</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIRUA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10878,13 +10878,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>1852.39</v>
+        <v>11507.79</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1057934-9-CM26</t>
+          <t>2665-104-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10904,17 +10904,17 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>61.607.202-1</t>
+          <t>69.150.101-9</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
+          <t>Dirección de Educación Municipal</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -10939,13 +10939,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1265.56</v>
+        <v>4620.73</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1084156-218-CM26</t>
+          <t>1057934-9-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10970,12 +10970,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>65.181.672-6</t>
+          <t>61.607.202-1</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
+          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>11527.07</v>
+        <v>1263.44</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1271.99</v>
+        <v>1287.65</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>3342.39</v>
+        <v>3383.52</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>11876.3</v>
+        <v>12034.4</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>4251</v>
+        <v>4306.48</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>1722.14</v>
+        <v>1754.71</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>2104.37</v>
+        <v>2144.17</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>22908.57</v>
+        <v>23169.09</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>4932.4</v>
+        <v>4988.49</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>6972.93</v>
+        <v>7035.74</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>3121.16</v>
+        <v>3141.12</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1657.21</v>
+        <v>1662.42</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>7506.7</v>
+        <v>7537.81</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>8948.35</v>
+        <v>8966.889999999999</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>4289.2</v>
+        <v>4270.78</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>9942.76</v>
+        <v>9807.58</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>10362.42</v>
+        <v>10221.54</v>
       </c>
     </row>
     <row r="190">
@@ -12037,13 +12037,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>2040.14</v>
+        <v>2022.74</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2672-10-CM26</t>
+          <t>2408-344-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12063,17 +12063,17 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>INGENIERIA INDUSTRIAL CABEZAS Y MORALES SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>76.156.518-4</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12098,13 +12098,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>31104.78</v>
+        <v>30596.59</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2408-344-CM26</t>
+          <t>2672-9-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12124,17 +12124,17 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SEGURYCEL SA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>99.510.910-7</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -12159,13 +12159,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>30859.81</v>
+        <v>19512.63</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2672-9-CM26</t>
+          <t>2672-10-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12205,12 +12205,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>SEGURYCEL SA</t>
+          <t>INGENIERIA INDUSTRIAL CABEZAS Y MORALES SPA</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>99.510.910-7</t>
+          <t>76.156.518-4</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>19680.49</v>
+        <v>30839.48</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>2118.6</v>
+        <v>2130.01</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1026.07</v>
+        <v>1031.6</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>13704.34</v>
+        <v>13778.13</v>
       </c>
     </row>
     <row r="197">
@@ -12464,13 +12464,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>4386.51</v>
+        <v>4410.13</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1084156-304-CM26</t>
+          <t>4081-162-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12490,17 +12490,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>65.181.672-6</t>
+          <t>69.151.001-8</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
+          <t>Ilustre Municipalidad de Cabrero</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
+          <t>COMERCIALIZADORA MERCEL SPA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>78.456.070-8</t>
+          <t>77.601.843-0</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -12525,13 +12525,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>1147.73</v>
+        <v>1488.98</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1084156-306-CM26</t>
+          <t>4454-381-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12551,17 +12551,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>65.181.672-6</t>
+          <t>69.150.600-2</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
+          <t>I MUNICIPALIDAD DE HUALQUI</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12571,12 +12571,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL PROMAC LIMITADA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.750.890-3</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -12586,13 +12586,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>9023.879999999999</v>
+        <v>8503.67</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1084156-308-CM26</t>
+          <t>3076-160-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>65.181.672-6</t>
+          <t>61.102.022-8</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
+          <t>CENTRO DE ABASTECIMIENTO (T)</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
@@ -12647,13 +12647,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>5781.17</v>
+        <v>3033.94</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1084156-310-CM26</t>
+          <t>1084156-311-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>76.967.556-6</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -12708,13 +12708,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>6774.47</v>
+        <v>5431</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1084156-311-CM26</t>
+          <t>1084156-304-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
+          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>76.967.556-6</t>
+          <t>78.456.070-8</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -12769,13 +12769,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>5370.94</v>
+        <v>1160.56</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>3076-160-CM26</t>
+          <t>1084156-308-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12800,12 +12800,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>61.102.022-8</t>
+          <t>65.181.672-6</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (T)</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12815,12 +12815,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -12830,13 +12830,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>3000.38</v>
+        <v>5845.82</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>4454-381-CM26</t>
+          <t>1084156-306-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12856,17 +12856,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>69.150.600-2</t>
+          <t>65.181.672-6</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUALQUI</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12876,12 +12876,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>COMERCIAL PROMAC LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>77.750.890-3</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -12891,13 +12891,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>8409.610000000001</v>
+        <v>9124.799999999999</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>4081-162-CM26</t>
+          <t>1084156-310-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12917,17 +12917,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>69.151.001-8</t>
+          <t>65.181.672-6</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -12937,12 +12937,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA MERCEL SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>77.601.843-0</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K205" t="inlineStr"/>
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1472.51</v>
+        <v>6850.23</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>3697.67</v>
+        <v>3725.68</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1119.53</v>
+        <v>1123.77</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>1748.89</v>
+        <v>1755.52</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>16332.52</v>
+        <v>16394.4</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>14236.41</v>
+        <v>14290.34</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>7793.23</v>
+        <v>7773.56</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1847.21</v>
+        <v>1864.76</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>906.54</v>
+        <v>915.15</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>2096.01</v>
+        <v>2115.93</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>1151.96</v>
+        <v>1162.9</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>8711.309999999999</v>
+        <v>8794.07</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>1645.21</v>
+        <v>1660.84</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>2927.73</v>
+        <v>2955.54</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>21935.72</v>
+        <v>22099.14</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>5848.47</v>
+        <v>5892.04</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>77301.66</v>
+        <v>76530.75</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>9467.58</v>
+        <v>9426.08</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>3468.86</v>
+        <v>3431.12</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>9747.82</v>
+        <v>9641.780000000001</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>1767.49</v>
+        <v>1748.26</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>4517.6</v>
+        <v>4468.46</v>
       </c>
     </row>
     <row r="227">
@@ -14294,13 +14294,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>13453.06</v>
+        <v>13419.84</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1084156-398-CM26</t>
+          <t>1084156-397-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>FERRETERIA CORONEL SPA</t>
+          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>76.196.593-k</t>
+          <t>14.205.876-6</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
@@ -14355,13 +14355,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>1498.31</v>
+        <v>2575.04</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1084156-397-CM26</t>
+          <t>1084156-398-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14401,12 +14401,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
+          <t>FERRETERIA CORONEL SPA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>14.205.876-6</t>
+          <t>76.196.593-k</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>2562.45</v>
+        <v>1505.67</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>4299.09</v>
+        <v>4320.21</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>4733.52</v>
+        <v>4758.69</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1223.74</v>
+        <v>1241.25</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>1762.11</v>
+        <v>1787.33</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>2776.01</v>
+        <v>2808.58</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>941.77</v>
+        <v>951.34</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>15271.42</v>
+        <v>15426.72</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>844.84</v>
+        <v>853.4299999999999</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>941.53</v>
+        <v>950.36</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>8815.450000000001</v>
+        <v>8898.129999999999</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>857.53</v>
+        <v>851.02</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>12606.26</v>
+        <v>12510.63</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>44590.69</v>
+        <v>44252.41</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>7061.32</v>
+        <v>6961.1</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>3751.29</v>
+        <v>3699.75</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1064.14</v>
+        <v>1057.55</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>1324.58</v>
+        <v>1316.37</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>2694.34</v>
+        <v>2706.58</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>9634.67</v>
+        <v>9678.42</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>810.63</v>
+        <v>814.3200000000001</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>5125.24</v>
+        <v>5201.56</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>4201.96</v>
+        <v>4264.52</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>2940.66</v>
+        <v>2996.57</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>4111.78</v>
+        <v>4189.95</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>5265.81</v>
+        <v>5365.92</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>1818.68</v>
+        <v>1853.26</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>6116.4</v>
+        <v>6232.69</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>2510.95</v>
+        <v>2558.69</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>1136.86</v>
+        <v>1158.47</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>15275.93</v>
+        <v>15620.45</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>16182.96</v>
+        <v>16547.93</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>793.08</v>
+        <v>810.96</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>944.75</v>
+        <v>951.27</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>1060.58</v>
+        <v>1067.91</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>20189.73</v>
+        <v>20329.12</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>9224.639999999999</v>
+        <v>9253.16</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>1975.38</v>
+        <v>1981.48</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>26039.71</v>
+        <v>25970.83</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>2207</v>
+        <v>2201.17</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>7574.3</v>
+        <v>7554.26</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>1116.88</v>
+        <v>1127.49</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>2907.09</v>
+        <v>2934.7</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>2949.2</v>
+        <v>2977.21</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>1721.55</v>
+        <v>1737.9</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>4425.51</v>
+        <v>4442.79</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>3220.24</v>
+        <v>3232.81</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>1341.77</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2039.48</v>
+        <v>2047.44</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>1667.45</v>
+        <v>1684.14</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>1907.53</v>
+        <v>1917.25</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>7741</v>
+        <v>7780.45</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>952.83</v>
+        <v>957.6900000000001</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>72531.69</v>
+        <v>72901.3</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>12760.88</v>
+        <v>12825.91</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>1333.46</v>
+        <v>1326.7</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>1216.96</v>
+        <v>1219.55</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>1124.7</v>
+        <v>1127.09</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>811.3099999999999</v>
+        <v>816.6</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>4014.94</v>
+        <v>4041.12</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>841.72</v>
+        <v>843.65</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>3296.72</v>
+        <v>3318.79</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>798.78</v>
+        <v>804.37</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>1376.81</v>
+        <v>1372.47</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>6111.57</v>
+        <v>6092.26</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>781</v>
+        <v>778.54</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>29789.87</v>
+        <v>29725.06</v>
       </c>
     </row>
     <row r="296">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>6436.74</v>
+        <v>6422.74</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>3031.09</v>
+        <v>3024.49</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>2913.84</v>
+        <v>2908</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>2259.96</v>
+        <v>2255.43</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>10141.07</v>
+        <v>10120.74</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>6883.69</v>
+        <v>6772.6</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>1867.63</v>
+        <v>1837.49</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>26758.66</v>
+        <v>26447.3</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>7265.02</v>
+        <v>7180.49</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>6527.1</v>
+        <v>6490.92</v>
       </c>
     </row>
     <row r="306">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>27208.18</v>
+        <v>27057.34</v>
       </c>
     </row>
     <row r="307">
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>3745.23</v>
+        <v>3724.47</v>
       </c>
     </row>
     <row r="308">
@@ -19235,13 +19235,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>781</v>
+        <v>776.67</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1063796-29-CM26</t>
+          <t>2408-696-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -19261,17 +19261,17 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>69.150.400-k</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
+          <t>COMERCIAL COMPARO LIMITADA</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>78.456.070-8</t>
+          <t>76.290.943-K</t>
         </is>
       </c>
       <c r="K309" t="inlineStr"/>
@@ -19296,13 +19296,13 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>4325.68</v>
+        <v>7712.26</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2408-696-CM26</t>
+          <t>1063796-29-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -19322,17 +19322,17 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>69.150.400-k</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -19342,12 +19342,12 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>COMERCIAL COMPARO LIMITADA</t>
+          <t>COMERCIAL CASTRO Y CASTRO LIMITADA</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>76.290.943-K</t>
+          <t>78.456.070-8</t>
         </is>
       </c>
       <c r="K310" t="inlineStr"/>
@@ -19357,7 +19357,68 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>7660.98</v>
+        <v>4354.63</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>1969-925-CM26</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>61.004.068-3</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr"/>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M311" s="2" t="n">
+        <v>1696.62</v>
       </c>
     </row>
   </sheetData>
